--- a/FIN302_AxisBank_Analysis.xlsx
+++ b/FIN302_AxisBank_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deore\OneDrive\Documents\MS Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE800C49-951F-4BFF-A7B0-4945C0DC5EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B415B15-2542-42D3-BF4F-022236AEEADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{BD6A6D98-F700-41D0-8D20-40EAE91D4823}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="9" activeTab="12" xr2:uid="{BD6A6D98-F700-41D0-8D20-40EAE91D4823}"/>
   </bookViews>
   <sheets>
     <sheet name="Income_Statement_Data" sheetId="1" r:id="rId1"/>
